--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/06,26/25,06,26 Останкино СЫР/Дв.Останкино Сыр от 22,06,26, Мелитополь.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/06,26/25,06,26 Останкино СЫР/Дв.Останкино Сыр от 22,06,26, Мелитополь.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\Заказы на отправку и сортировку\Останкино\Останкино исходники\СЫРЫ\Мелитополь\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\06,26\25,06,26 Останкино СЫР\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B86A617C-8444-4C4C-A520-3DDA63EB57B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E188A10-DEBF-47DE-A4DA-2076EFDC1FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="85">
   <si>
     <t>Ведомость по товарам на складах</t>
   </si>
@@ -274,9 +274,6 @@
     <t>15,06,</t>
   </si>
   <si>
-    <t>итого</t>
-  </si>
-  <si>
     <t>ТК</t>
   </si>
   <si>
@@ -284,6 +281,9 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>заказ</t>
   </si>
 </sst>
 </file>
@@ -293,7 +293,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0_ ;[Red]\-0\ "/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="8"/>
       <name val="Arial"/>
@@ -330,6 +330,32 @@
       <b/>
       <sz val="8"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
     </font>
@@ -439,7 +465,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -498,6 +524,26 @@
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{5463827A-44DB-4451-9410-79EAFA46024A}"/>
@@ -7056,16 +7102,28 @@
     <col min="10" max="10" width="3.5" customWidth="1"/>
     <col min="11" max="12" width="8.5" customWidth="1"/>
     <col min="13" max="14" width="1.1640625" customWidth="1"/>
-    <col min="15" max="30" width="8.5" customWidth="1"/>
+    <col min="15" max="16" width="8.5" customWidth="1"/>
+    <col min="17" max="17" width="8.5" style="29" customWidth="1"/>
+    <col min="18" max="18" width="8.5" style="25" customWidth="1"/>
+    <col min="19" max="19" width="8.5" style="29" customWidth="1"/>
+    <col min="20" max="30" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" s="1" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1" spans="1:54" s="1" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q1" s="28"/>
+      <c r="R1" s="24"/>
+      <c r="S1" s="28"/>
+    </row>
     <row r="2" spans="1:54" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:54" s="1" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:54" s="1" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q3" s="28"/>
+      <c r="R3" s="24"/>
+      <c r="S3" s="28"/>
+    </row>
     <row r="4" spans="1:54" ht="12.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>1</v>
@@ -7087,7 +7145,11 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="1:54" s="1" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:54" s="1" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q7" s="28"/>
+      <c r="R7" s="24"/>
+      <c r="S7" s="28"/>
+    </row>
     <row r="8" spans="1:54" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>3</v>
@@ -7137,13 +7199,13 @@
       <c r="P8" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="Q8" s="14" t="s">
+      <c r="Q8" s="30" t="s">
         <v>66</v>
       </c>
       <c r="R8" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="S8" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="S8" s="31" t="s">
         <v>67</v>
       </c>
       <c r="T8" s="15" t="s">
@@ -7182,7 +7244,7 @@
     </row>
     <row r="9" spans="1:54" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="5"/>
@@ -7206,7 +7268,9 @@
       <c r="Q9" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="R9" s="16"/>
+      <c r="R9" s="26" t="s">
+        <v>76</v>
+      </c>
       <c r="S9" s="16" t="s">
         <v>76</v>
       </c>
@@ -7230,15 +7294,15 @@
         <v>75</v>
       </c>
       <c r="AC9" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="AD9" s="16" t="s">
         <v>82</v>
-      </c>
-      <c r="AD9" s="16" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:54" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="19">
@@ -7282,15 +7346,15 @@
         <f t="shared" si="1"/>
         <v>423.77440000000007</v>
       </c>
-      <c r="Q10" s="19">
+      <c r="Q10" s="32">
         <f t="shared" si="1"/>
         <v>1127.7979999999998</v>
       </c>
-      <c r="R10" s="19">
+      <c r="R10" s="27">
         <f t="shared" si="1"/>
         <v>1280.3899999999999</v>
       </c>
-      <c r="S10" s="19">
+      <c r="S10" s="32">
         <f t="shared" si="1"/>
         <v>673</v>
       </c>
@@ -7377,7 +7441,7 @@
         <f>E11/5</f>
         <v>12.39</v>
       </c>
-      <c r="Q11" s="20">
+      <c r="Q11" s="33">
         <f>P11*20-F11-O11</f>
         <v>37.256</v>
       </c>
@@ -7385,7 +7449,7 @@
         <f>Q11</f>
         <v>37.256</v>
       </c>
-      <c r="S11" s="20">
+      <c r="S11" s="33">
         <f>VLOOKUP(A11,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -7504,7 +7568,7 @@
         <f t="shared" ref="P12:P55" si="3">E12/5</f>
         <v>16.388399999999997</v>
       </c>
-      <c r="Q12" s="20">
+      <c r="Q12" s="33">
         <f t="shared" ref="Q12:Q50" si="4">P12*20-F12-O12</f>
         <v>273.4079999999999</v>
       </c>
@@ -7512,7 +7576,7 @@
         <f>S12</f>
         <v>350</v>
       </c>
-      <c r="S12" s="20">
+      <c r="S12" s="33">
         <f>VLOOKUP(A12,[3]TDSheet!$A:$R,18,0)</f>
         <v>350</v>
       </c>
@@ -7632,12 +7696,12 @@
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="Q13" s="20"/>
+      <c r="Q13" s="33"/>
       <c r="R13" s="20">
         <f t="shared" ref="R13:R55" si="10">Q13</f>
         <v>0</v>
       </c>
-      <c r="S13" s="20">
+      <c r="S13" s="33">
         <f>VLOOKUP(A13,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -7757,12 +7821,12 @@
         <f t="shared" si="3"/>
         <v>8.6</v>
       </c>
-      <c r="Q14" s="20"/>
+      <c r="Q14" s="33"/>
       <c r="R14" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S14" s="20">
+      <c r="S14" s="33">
         <f>VLOOKUP(A14,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -7882,12 +7946,12 @@
         <f t="shared" si="3"/>
         <v>19.600000000000001</v>
       </c>
-      <c r="Q15" s="20"/>
+      <c r="Q15" s="33"/>
       <c r="R15" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S15" s="20">
+      <c r="S15" s="33">
         <f>VLOOKUP(A15,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -8007,12 +8071,12 @@
         <f t="shared" si="3"/>
         <v>43.4</v>
       </c>
-      <c r="Q16" s="20"/>
+      <c r="Q16" s="33"/>
       <c r="R16" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S16" s="20">
+      <c r="S16" s="33">
         <f>VLOOKUP(A16,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -8132,12 +8196,12 @@
         <f t="shared" si="3"/>
         <v>24.2</v>
       </c>
-      <c r="Q17" s="20"/>
+      <c r="Q17" s="33"/>
       <c r="R17" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S17" s="20">
+      <c r="S17" s="33">
         <f>VLOOKUP(A17,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -8254,12 +8318,12 @@
         <f t="shared" si="3"/>
         <v>5.8</v>
       </c>
-      <c r="Q18" s="20"/>
+      <c r="Q18" s="33"/>
       <c r="R18" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S18" s="20">
+      <c r="S18" s="33">
         <f>VLOOKUP(A18,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -8377,12 +8441,12 @@
         <f t="shared" si="3"/>
         <v>6.4</v>
       </c>
-      <c r="Q19" s="20"/>
+      <c r="Q19" s="33"/>
       <c r="R19" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S19" s="20">
+      <c r="S19" s="33">
         <f>VLOOKUP(A19,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -8500,12 +8564,12 @@
         <f t="shared" si="3"/>
         <v>6.4</v>
       </c>
-      <c r="Q20" s="20"/>
+      <c r="Q20" s="33"/>
       <c r="R20" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S20" s="20">
+      <c r="S20" s="33">
         <f>VLOOKUP(A20,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -8624,12 +8688,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q21" s="20"/>
+      <c r="Q21" s="33"/>
       <c r="R21" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S21" s="20">
+      <c r="S21" s="33">
         <f>VLOOKUP(A21,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -8746,12 +8810,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q22" s="20"/>
+      <c r="Q22" s="33"/>
       <c r="R22" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S22" s="20">
+      <c r="S22" s="33">
         <f>VLOOKUP(A22,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -8867,12 +8931,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q23" s="20"/>
+      <c r="Q23" s="33"/>
       <c r="R23" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S23" s="20">
+      <c r="S23" s="33">
         <f>VLOOKUP(A23,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -8990,12 +9054,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q24" s="20"/>
+      <c r="Q24" s="33"/>
       <c r="R24" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S24" s="20">
+      <c r="S24" s="33">
         <f>VLOOKUP(A24,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -9115,12 +9179,12 @@
         <f t="shared" si="3"/>
         <v>3.8</v>
       </c>
-      <c r="Q25" s="20"/>
+      <c r="Q25" s="33"/>
       <c r="R25" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S25" s="20">
+      <c r="S25" s="33">
         <f>VLOOKUP(A25,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -9237,12 +9301,12 @@
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
-      <c r="Q26" s="20"/>
+      <c r="Q26" s="33"/>
       <c r="R26" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S26" s="20">
+      <c r="S26" s="33">
         <f>VLOOKUP(A26,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -9362,7 +9426,7 @@
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="Q27" s="20">
+      <c r="Q27" s="33">
         <f t="shared" si="4"/>
         <v>73</v>
       </c>
@@ -9370,7 +9434,7 @@
         <f>S27</f>
         <v>73</v>
       </c>
-      <c r="S27" s="20">
+      <c r="S27" s="33">
         <f>VLOOKUP(A27,[3]TDSheet!$A:$R,18,0)</f>
         <v>73</v>
       </c>
@@ -9487,12 +9551,12 @@
         <f t="shared" si="3"/>
         <v>1.3220000000000001</v>
       </c>
-      <c r="Q28" s="20"/>
+      <c r="Q28" s="33"/>
       <c r="R28" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S28" s="20">
+      <c r="S28" s="33">
         <f>VLOOKUP(A28,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -9610,12 +9674,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q29" s="20"/>
+      <c r="Q29" s="33"/>
       <c r="R29" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S29" s="20">
+      <c r="S29" s="33">
         <f>VLOOKUP(A29,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -9732,12 +9796,12 @@
         <f t="shared" si="3"/>
         <v>2.29</v>
       </c>
-      <c r="Q30" s="20"/>
+      <c r="Q30" s="33"/>
       <c r="R30" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S30" s="20">
+      <c r="S30" s="33">
         <f>VLOOKUP(A30,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -9854,12 +9918,12 @@
         <f t="shared" si="3"/>
         <v>2.2000000000000002</v>
       </c>
-      <c r="Q31" s="20"/>
+      <c r="Q31" s="33"/>
       <c r="R31" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S31" s="20">
+      <c r="S31" s="33">
         <f>VLOOKUP(A31,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -9976,12 +10040,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q32" s="20"/>
+      <c r="Q32" s="33"/>
       <c r="R32" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S32" s="20">
+      <c r="S32" s="33">
         <f>VLOOKUP(A32,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -10100,12 +10164,12 @@
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="Q33" s="20"/>
+      <c r="Q33" s="33"/>
       <c r="R33" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S33" s="20">
+      <c r="S33" s="33">
         <f>VLOOKUP(A33,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -10224,12 +10288,12 @@
         <f t="shared" si="3"/>
         <v>3.6</v>
       </c>
-      <c r="Q34" s="20"/>
+      <c r="Q34" s="33"/>
       <c r="R34" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S34" s="20">
+      <c r="S34" s="33">
         <f>VLOOKUP(A34,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -10349,12 +10413,12 @@
         <f t="shared" si="3"/>
         <v>6.2</v>
       </c>
-      <c r="Q35" s="20"/>
+      <c r="Q35" s="33"/>
       <c r="R35" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S35" s="20">
+      <c r="S35" s="33">
         <f>VLOOKUP(A35,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -10472,12 +10536,12 @@
         <f t="shared" si="3"/>
         <v>3.2</v>
       </c>
-      <c r="Q36" s="20"/>
+      <c r="Q36" s="33"/>
       <c r="R36" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S36" s="20">
+      <c r="S36" s="33">
         <f>VLOOKUP(A36,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -10597,12 +10661,12 @@
         <f t="shared" si="3"/>
         <v>29.6</v>
       </c>
-      <c r="Q37" s="20"/>
+      <c r="Q37" s="33"/>
       <c r="R37" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S37" s="20">
+      <c r="S37" s="33">
         <f>VLOOKUP(A37,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -10722,12 +10786,12 @@
         <f t="shared" si="3"/>
         <v>53.8</v>
       </c>
-      <c r="Q38" s="20"/>
+      <c r="Q38" s="33"/>
       <c r="R38" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S38" s="20">
+      <c r="S38" s="33">
         <f>VLOOKUP(A38,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -10847,12 +10911,12 @@
         <f t="shared" si="3"/>
         <v>31.8</v>
       </c>
-      <c r="Q39" s="20"/>
+      <c r="Q39" s="33"/>
       <c r="R39" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S39" s="20">
+      <c r="S39" s="33">
         <f>VLOOKUP(A39,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -10972,12 +11036,12 @@
         <f t="shared" si="3"/>
         <v>9.1999999999999993</v>
       </c>
-      <c r="Q40" s="20"/>
+      <c r="Q40" s="33"/>
       <c r="R40" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S40" s="20">
+      <c r="S40" s="33">
         <f>VLOOKUP(A40,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -11095,7 +11159,7 @@
         <f t="shared" si="3"/>
         <v>12.5824</v>
       </c>
-      <c r="Q41" s="20">
+      <c r="Q41" s="33">
         <f t="shared" si="4"/>
         <v>126.002</v>
       </c>
@@ -11103,7 +11167,7 @@
         <f t="shared" si="10"/>
         <v>126.002</v>
       </c>
-      <c r="S41" s="20">
+      <c r="S41" s="33">
         <f>VLOOKUP(A41,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -11220,7 +11284,7 @@
         <f t="shared" si="3"/>
         <v>7.7087999999999992</v>
       </c>
-      <c r="Q42" s="20">
+      <c r="Q42" s="33">
         <f t="shared" si="4"/>
         <v>56.745999999999981</v>
       </c>
@@ -11228,7 +11292,7 @@
         <f t="shared" si="10"/>
         <v>56.745999999999981</v>
       </c>
-      <c r="S42" s="20">
+      <c r="S42" s="33">
         <f>VLOOKUP(A42,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -11348,12 +11412,12 @@
         <f t="shared" si="3"/>
         <v>2.5036</v>
       </c>
-      <c r="Q43" s="20"/>
+      <c r="Q43" s="33"/>
       <c r="R43" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S43" s="20">
+      <c r="S43" s="33">
         <f>VLOOKUP(A43,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -11470,7 +11534,7 @@
         <f t="shared" si="3"/>
         <v>8.595600000000001</v>
       </c>
-      <c r="Q44" s="20">
+      <c r="Q44" s="33">
         <f t="shared" si="4"/>
         <v>130.38600000000002</v>
       </c>
@@ -11478,7 +11542,7 @@
         <f t="shared" si="10"/>
         <v>130.38600000000002</v>
       </c>
-      <c r="S44" s="20">
+      <c r="S44" s="33">
         <f>VLOOKUP(A44,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -11596,7 +11660,7 @@
         <f t="shared" si="3"/>
         <v>13.8</v>
       </c>
-      <c r="Q45" s="20">
+      <c r="Q45" s="33">
         <f t="shared" si="4"/>
         <v>174</v>
       </c>
@@ -11604,7 +11668,7 @@
         <f>S45</f>
         <v>250</v>
       </c>
-      <c r="S45" s="20">
+      <c r="S45" s="33">
         <f>VLOOKUP(A45,[3]TDSheet!$A:$R,18,0)</f>
         <v>250</v>
       </c>
@@ -11724,7 +11788,7 @@
         <f t="shared" si="3"/>
         <v>12.6</v>
       </c>
-      <c r="Q46" s="20">
+      <c r="Q46" s="33">
         <f t="shared" si="4"/>
         <v>30</v>
       </c>
@@ -11732,7 +11796,7 @@
         <f t="shared" si="10"/>
         <v>30</v>
       </c>
-      <c r="S46" s="20">
+      <c r="S46" s="33">
         <f>VLOOKUP(A46,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -11850,12 +11914,12 @@
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="Q47" s="20"/>
+      <c r="Q47" s="33"/>
       <c r="R47" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S47" s="20">
+      <c r="S47" s="33">
         <f>VLOOKUP(A47,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -11975,12 +12039,12 @@
         <f t="shared" si="3"/>
         <v>12.8</v>
       </c>
-      <c r="Q48" s="20"/>
+      <c r="Q48" s="33"/>
       <c r="R48" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S48" s="20">
+      <c r="S48" s="33">
         <f>VLOOKUP(A48,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -12096,12 +12160,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q49" s="20"/>
+      <c r="Q49" s="33"/>
       <c r="R49" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S49" s="20">
+      <c r="S49" s="33">
         <f>VLOOKUP(A49,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -12218,7 +12282,7 @@
         <f t="shared" si="3"/>
         <v>16.600000000000001</v>
       </c>
-      <c r="Q50" s="20">
+      <c r="Q50" s="33">
         <f t="shared" si="4"/>
         <v>227</v>
       </c>
@@ -12226,7 +12290,7 @@
         <f t="shared" si="10"/>
         <v>227</v>
       </c>
-      <c r="S50" s="20">
+      <c r="S50" s="33">
         <f>VLOOKUP(A50,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -12343,12 +12407,12 @@
         <f t="shared" si="3"/>
         <v>1.9487999999999999</v>
       </c>
-      <c r="Q51" s="20"/>
+      <c r="Q51" s="33"/>
       <c r="R51" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S51" s="20">
+      <c r="S51" s="33">
         <f>VLOOKUP(A51,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -12468,12 +12532,12 @@
         <f t="shared" si="3"/>
         <v>1.8716000000000002</v>
       </c>
-      <c r="Q52" s="20"/>
+      <c r="Q52" s="33"/>
       <c r="R52" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S52" s="20">
+      <c r="S52" s="33">
         <f>VLOOKUP(A52,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -12590,12 +12654,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q53" s="20"/>
+      <c r="Q53" s="33"/>
       <c r="R53" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S53" s="20">
+      <c r="S53" s="33">
         <f>VLOOKUP(A53,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -12712,12 +12776,12 @@
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="Q54" s="20"/>
+      <c r="Q54" s="33"/>
       <c r="R54" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S54" s="20">
+      <c r="S54" s="33">
         <f>VLOOKUP(A54,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -12836,12 +12900,12 @@
         <f t="shared" si="3"/>
         <v>8.9732000000000003</v>
       </c>
-      <c r="Q55" s="20"/>
+      <c r="Q55" s="33"/>
       <c r="R55" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S55" s="20">
+      <c r="S55" s="33">
         <f>VLOOKUP(A55,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
